--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/72.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/72.xlsx
@@ -426,13 +426,13 @@
         <v>-2.352188093797831</v>
       </c>
       <c r="E2">
-        <v>-6.925715145526005</v>
+        <v>-12.7545188133</v>
       </c>
       <c r="F2">
-        <v>-2.96821036679571</v>
+        <v>-3.627720873106356</v>
       </c>
       <c r="G2">
-        <v>-8.607444231354634</v>
+        <v>-10.19406420947814</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.863040914540538</v>
       </c>
       <c r="E3">
-        <v>-8.391973178066124</v>
+        <v>-13.16197376353363</v>
       </c>
       <c r="F3">
-        <v>-2.832294328446576</v>
+        <v>-3.738076806874709</v>
       </c>
       <c r="G3">
-        <v>-8.335844555424233</v>
+        <v>-9.823854099596796</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.358584414952168</v>
       </c>
       <c r="E4">
-        <v>-7.863339981007972</v>
+        <v>-13.66472830082677</v>
       </c>
       <c r="F4">
-        <v>-2.865740490702009</v>
+        <v>-3.745757429433466</v>
       </c>
       <c r="G4">
-        <v>-8.115266661037957</v>
+        <v>-9.009424492165232</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.9387053569785032</v>
       </c>
       <c r="E5">
-        <v>-8.202038517759064</v>
+        <v>-14.12779475069985</v>
       </c>
       <c r="F5">
-        <v>-2.385283255241281</v>
+        <v>-3.488683546383473</v>
       </c>
       <c r="G5">
-        <v>-8.309250205646856</v>
+        <v>-9.28445990797754</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.6146202609222212</v>
       </c>
       <c r="E6">
-        <v>-10.32074943658445</v>
+        <v>-15.03910899243903</v>
       </c>
       <c r="F6">
-        <v>-2.203634709318392</v>
+        <v>-3.534343157625782</v>
       </c>
       <c r="G6">
-        <v>-7.620385664697182</v>
+        <v>-8.601370334063409</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.4131307237873315</v>
       </c>
       <c r="E7">
-        <v>-11.4232899873527</v>
+        <v>-15.58518152385014</v>
       </c>
       <c r="F7">
-        <v>-2.594035154216368</v>
+        <v>-3.222915119073697</v>
       </c>
       <c r="G7">
-        <v>-8.303963447849853</v>
+        <v>-8.725641776600401</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.3292719822124515</v>
       </c>
       <c r="E8">
-        <v>-11.45637862197762</v>
+        <v>-15.69448573949698</v>
       </c>
       <c r="F8">
-        <v>-2.460117966410189</v>
+        <v>-3.662499878512893</v>
       </c>
       <c r="G8">
-        <v>-7.553226870835385</v>
+        <v>-8.147421896794404</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.3534763197420819</v>
       </c>
       <c r="E9">
-        <v>-11.62646093215199</v>
+        <v>-17.19591316553574</v>
       </c>
       <c r="F9">
-        <v>-2.40928023053298</v>
+        <v>-3.195584793353133</v>
       </c>
       <c r="G9">
-        <v>-6.811297640699038</v>
+        <v>-7.976576076124246</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.4598083739606552</v>
       </c>
       <c r="E10">
-        <v>-12.66760455990531</v>
+        <v>-17.0042923014308</v>
       </c>
       <c r="F10">
-        <v>-2.205766098645795</v>
+        <v>-3.184730695274251</v>
       </c>
       <c r="G10">
-        <v>-6.494502059779578</v>
+        <v>-7.020008395546407</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.6282897121281739</v>
       </c>
       <c r="E11">
-        <v>-13.6562017579769</v>
+        <v>-17.72393584052914</v>
       </c>
       <c r="F11">
-        <v>-2.190230896373693</v>
+        <v>-3.094096532631748</v>
       </c>
       <c r="G11">
-        <v>-5.846243734827785</v>
+        <v>-6.704573012558917</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.8422878994920546</v>
       </c>
       <c r="E12">
-        <v>-14.43653202095363</v>
+        <v>-18.26004481797199</v>
       </c>
       <c r="F12">
-        <v>-1.915635386019685</v>
+        <v>-3.358241359832038</v>
       </c>
       <c r="G12">
-        <v>-5.074961903253551</v>
+        <v>-5.971969362102027</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.096576899451365</v>
       </c>
       <c r="E13">
-        <v>-15.2990169571468</v>
+        <v>-20.04767003640469</v>
       </c>
       <c r="F13">
-        <v>-2.11192946762407</v>
+        <v>-3.137586649646125</v>
       </c>
       <c r="G13">
-        <v>-5.487639690026238</v>
+        <v>-6.015918636548829</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.389887382284757</v>
       </c>
       <c r="E14">
-        <v>-16.16514425967184</v>
+        <v>-20.34376493138569</v>
       </c>
       <c r="F14">
-        <v>-1.846298549303158</v>
+        <v>-2.816624102287817</v>
       </c>
       <c r="G14">
-        <v>-4.823406218921422</v>
+        <v>-5.207710433477889</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.714063089983269</v>
       </c>
       <c r="E15">
-        <v>-16.36527505378136</v>
+        <v>-21.3340732525231</v>
       </c>
       <c r="F15">
-        <v>-1.561833869712197</v>
+        <v>-2.959252401701836</v>
       </c>
       <c r="G15">
-        <v>-4.920977576525098</v>
+        <v>-4.52414439867588</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.04969872374694</v>
       </c>
       <c r="E16">
-        <v>-17.98641879625831</v>
+        <v>-22.044006583544</v>
       </c>
       <c r="F16">
-        <v>-0.5730531193605666</v>
+        <v>-2.531418033871351</v>
       </c>
       <c r="G16">
-        <v>-3.753932972384002</v>
+        <v>-4.836971647816847</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.364950746244207</v>
       </c>
       <c r="E17">
-        <v>-19.13227734114453</v>
+        <v>-22.62443863224541</v>
       </c>
       <c r="F17">
-        <v>-1.161617271091046</v>
+        <v>-2.411855624788284</v>
       </c>
       <c r="G17">
-        <v>-3.515331802712977</v>
+        <v>-3.770498146814616</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.624949318790361</v>
       </c>
       <c r="E18">
-        <v>-20.24652164142615</v>
+        <v>-22.8523834825973</v>
       </c>
       <c r="F18">
-        <v>-1.197609834742685</v>
+        <v>-2.447916942934355</v>
       </c>
       <c r="G18">
-        <v>-3.061174505876683</v>
+        <v>-4.808444041669752</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.797248715967064</v>
       </c>
       <c r="E19">
-        <v>-19.94084528791877</v>
+        <v>-24.14742953148269</v>
       </c>
       <c r="F19">
-        <v>-0.2819689558538342</v>
+        <v>-1.979409735626413</v>
       </c>
       <c r="G19">
-        <v>-2.308016463253958</v>
+        <v>-4.255723304285158</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.859782765457414</v>
       </c>
       <c r="E20">
-        <v>-21.76556283669352</v>
+        <v>-25.47643638937119</v>
       </c>
       <c r="F20">
-        <v>-0.8542896511828183</v>
+        <v>-1.895232696888733</v>
       </c>
       <c r="G20">
-        <v>-2.655240272382843</v>
+        <v>-3.747145036447108</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.804625836974613</v>
       </c>
       <c r="E21">
-        <v>-22.27980100329981</v>
+        <v>-25.92904089991703</v>
       </c>
       <c r="F21">
-        <v>-0.1918160746723585</v>
+        <v>-1.354575517164357</v>
       </c>
       <c r="G21">
-        <v>-2.196824851118443</v>
+        <v>-3.945681719622908</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.639300054033888</v>
       </c>
       <c r="E22">
-        <v>-22.6427709070332</v>
+        <v>-26.25392170259042</v>
       </c>
       <c r="F22">
-        <v>-0.153753420881124</v>
+        <v>-1.584677757579198</v>
       </c>
       <c r="G22">
-        <v>-2.51760181753935</v>
+        <v>-3.888921521467514</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.386522246920261</v>
       </c>
       <c r="E23">
-        <v>-21.94264746116156</v>
+        <v>-26.68387459857065</v>
       </c>
       <c r="F23">
-        <v>-0.2997705713399956</v>
+        <v>-1.235232625443033</v>
       </c>
       <c r="G23">
-        <v>-1.340054187908205</v>
+        <v>-3.524654771647842</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.079465818023975</v>
       </c>
       <c r="E24">
-        <v>-21.97580670037899</v>
+        <v>-26.55610935858495</v>
       </c>
       <c r="F24">
-        <v>0.2043373818380603</v>
+        <v>-1.156323175019754</v>
       </c>
       <c r="G24">
-        <v>-1.04775261274257</v>
+        <v>-3.816107854821365</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.754976453995006</v>
       </c>
       <c r="E25">
-        <v>-24.06030346431043</v>
+        <v>-27.00235114938115</v>
       </c>
       <c r="F25">
-        <v>0.400433483633176</v>
+        <v>-1.172931113078482</v>
       </c>
       <c r="G25">
-        <v>-2.06007666018052</v>
+        <v>-3.679735611104562</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.448177937334552</v>
       </c>
       <c r="E26">
-        <v>-23.19384805809073</v>
+        <v>-27.02449191895381</v>
       </c>
       <c r="F26">
-        <v>0.5424637017823737</v>
+        <v>-0.8828857222948601</v>
       </c>
       <c r="G26">
-        <v>-1.663214764140798</v>
+        <v>-3.325971886774939</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.185574073864549</v>
       </c>
       <c r="E27">
-        <v>-23.29781539718516</v>
+        <v>-27.47421410084022</v>
       </c>
       <c r="F27">
-        <v>0.9468113686412851</v>
+        <v>-0.8059237636355635</v>
       </c>
       <c r="G27">
-        <v>-2.510440545125926</v>
+        <v>-3.735467175891058</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.9851637280646466</v>
       </c>
       <c r="E28">
-        <v>-22.50300288631875</v>
+        <v>-27.3613339702427</v>
       </c>
       <c r="F28">
-        <v>0.6251206863359168</v>
+        <v>-1.159246483584234</v>
       </c>
       <c r="G28">
-        <v>-1.59668777047005</v>
+        <v>-3.504792226798652</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.8556310177432394</v>
       </c>
       <c r="E29">
-        <v>-22.22212951084324</v>
+        <v>-26.73802001461244</v>
       </c>
       <c r="F29">
-        <v>-0.1866048153413468</v>
+        <v>-1.270739765796631</v>
       </c>
       <c r="G29">
-        <v>-1.727125791731252</v>
+        <v>-3.287424242887151</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.7964767994854071</v>
       </c>
       <c r="E30">
-        <v>-22.64905471576767</v>
+        <v>-26.43743134497797</v>
       </c>
       <c r="F30">
-        <v>-0.1248616226062828</v>
+        <v>-0.9290183313241673</v>
       </c>
       <c r="G30">
-        <v>-1.989641381856875</v>
+        <v>-3.3300080979128</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.8017323694300734</v>
       </c>
       <c r="E31">
-        <v>-22.51181184753871</v>
+        <v>-27.48054359489926</v>
       </c>
       <c r="F31">
-        <v>0.2975287146530047</v>
+        <v>-0.8892235612936791</v>
       </c>
       <c r="G31">
-        <v>-1.880619298476575</v>
+        <v>-2.946453167053983</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.8580248662655463</v>
       </c>
       <c r="E32">
-        <v>-23.11639066688268</v>
+        <v>-26.13025983539365</v>
       </c>
       <c r="F32">
-        <v>0.2788407460458479</v>
+        <v>-0.9538544427949021</v>
       </c>
       <c r="G32">
-        <v>-2.595882383359291</v>
+        <v>-3.66453324535051</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.9492961714839427</v>
       </c>
       <c r="E33">
-        <v>-21.37519419785023</v>
+        <v>-25.66707709560347</v>
       </c>
       <c r="F33">
-        <v>0.5548295703713647</v>
+        <v>-0.9232164460349596</v>
       </c>
       <c r="G33">
-        <v>-1.774526470527505</v>
+        <v>-3.395232330032584</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.056134894104318</v>
       </c>
       <c r="E34">
-        <v>-19.92527489866199</v>
+        <v>-26.26098216184263</v>
       </c>
       <c r="F34">
-        <v>0.1086866262042042</v>
+        <v>-0.9387756709617426</v>
       </c>
       <c r="G34">
-        <v>-1.725031974569179</v>
+        <v>-3.095014977266693</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.160784814342915</v>
       </c>
       <c r="E35">
-        <v>-19.62997742025536</v>
+        <v>-25.23228570842982</v>
       </c>
       <c r="F35">
-        <v>0.2277826644394947</v>
+        <v>-0.9034789359284557</v>
       </c>
       <c r="G35">
-        <v>-2.080803361489369</v>
+        <v>-3.27053533612724</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.249248195635421</v>
       </c>
       <c r="E36">
-        <v>-19.57718179789413</v>
+        <v>-23.5772725275989</v>
       </c>
       <c r="F36">
-        <v>0.0975881597414964</v>
+        <v>-0.9205557299371675</v>
       </c>
       <c r="G36">
-        <v>-2.504986699675091</v>
+        <v>-3.908222756229615</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.312326868996686</v>
       </c>
       <c r="E37">
-        <v>-19.21429911159857</v>
+        <v>-23.250198829346</v>
       </c>
       <c r="F37">
-        <v>0.3364387882973031</v>
+        <v>-1.109104576325377</v>
       </c>
       <c r="G37">
-        <v>-1.178112311666039</v>
+        <v>-3.361846128201427</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.347714347399907</v>
       </c>
       <c r="E38">
-        <v>-19.68156861133238</v>
+        <v>-22.98144037130502</v>
       </c>
       <c r="F38">
-        <v>-0.5328019188911358</v>
+        <v>-0.7986515262063867</v>
       </c>
       <c r="G38">
-        <v>-2.792518444472762</v>
+        <v>-3.629139380928787</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.357179624180906</v>
       </c>
       <c r="E39">
-        <v>-17.38386674404086</v>
+        <v>-22.48469968401023</v>
       </c>
       <c r="F39">
-        <v>0.08885302547897563</v>
+        <v>-0.7860926480125434</v>
       </c>
       <c r="G39">
-        <v>-2.328570855419793</v>
+        <v>-3.561025054546641</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.348517922938105</v>
       </c>
       <c r="E40">
-        <v>-18.0210275062281</v>
+        <v>-21.67341553702954</v>
       </c>
       <c r="F40">
-        <v>0.2468110920492022</v>
+        <v>-0.5019410912998402</v>
       </c>
       <c r="G40">
-        <v>-2.414472184701193</v>
+        <v>-3.823710343070687</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.331184049368886</v>
       </c>
       <c r="E41">
-        <v>-15.76585452290283</v>
+        <v>-20.59685747630942</v>
       </c>
       <c r="F41">
-        <v>0.3668208195297805</v>
+        <v>-0.5035083624259369</v>
       </c>
       <c r="G41">
-        <v>-2.692456436529163</v>
+        <v>-3.744228834738834</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.319127224858318</v>
       </c>
       <c r="E42">
-        <v>-16.6465388311214</v>
+        <v>-20.32203117652286</v>
       </c>
       <c r="F42">
-        <v>0.5990966960095675</v>
+        <v>-0.5915803846915803</v>
       </c>
       <c r="G42">
-        <v>-2.046252767570575</v>
+        <v>-4.311541023643159</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.325111279977816</v>
       </c>
       <c r="E43">
-        <v>-16.31022839088208</v>
+        <v>-19.41314241019738</v>
       </c>
       <c r="F43">
-        <v>0.101977678608931</v>
+        <v>-0.8288653988560959</v>
       </c>
       <c r="G43">
-        <v>-2.738050480068365</v>
+        <v>-4.171834859083506</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.362341347930404</v>
       </c>
       <c r="E44">
-        <v>-14.55288423621871</v>
+        <v>-18.52584618954969</v>
       </c>
       <c r="F44">
-        <v>-0.18719461293214</v>
+        <v>-0.7710321002622456</v>
       </c>
       <c r="G44">
-        <v>-2.602732977166372</v>
+        <v>-4.146633341545489</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.442697501858741</v>
       </c>
       <c r="E45">
-        <v>-12.97263716565734</v>
+        <v>-18.87475331973721</v>
       </c>
       <c r="F45">
-        <v>-0.01530009317721462</v>
+        <v>-0.5974245167183307</v>
       </c>
       <c r="G45">
-        <v>-3.114995005622483</v>
+        <v>-4.067942888824744</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.572252192851576</v>
       </c>
       <c r="E46">
-        <v>-14.37818355505112</v>
+        <v>-18.06684573356361</v>
       </c>
       <c r="F46">
-        <v>0.2807078861717579</v>
+        <v>-0.4127573999796398</v>
       </c>
       <c r="G46">
-        <v>-2.822479349400377</v>
+        <v>-4.26410118367804</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.759399280593113</v>
       </c>
       <c r="E47">
-        <v>-12.92365419129232</v>
+        <v>-16.45121330251471</v>
       </c>
       <c r="F47">
-        <v>0.1836903243232826</v>
+        <v>-0.511940314219033</v>
       </c>
       <c r="G47">
-        <v>-2.636764032911534</v>
+        <v>-5.181725692562538</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.004590179345941</v>
       </c>
       <c r="E48">
-        <v>-12.16006967637729</v>
+        <v>-16.78900643919699</v>
       </c>
       <c r="F48">
-        <v>0.1926880510524908</v>
+        <v>-0.6364041732244643</v>
       </c>
       <c r="G48">
-        <v>-3.220839812835398</v>
+        <v>-5.317868190755322</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.310512905632714</v>
       </c>
       <c r="E49">
-        <v>-12.60811811409979</v>
+        <v>-15.82153247392348</v>
       </c>
       <c r="F49">
-        <v>0.3354894792536948</v>
+        <v>-0.6473651306983074</v>
       </c>
       <c r="G49">
-        <v>-3.360945421317493</v>
+        <v>-5.3992816500846</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.67540868193066</v>
       </c>
       <c r="E50">
-        <v>-11.84074587045652</v>
+        <v>-14.87684302597798</v>
       </c>
       <c r="F50">
-        <v>-0.0527099934550431</v>
+        <v>-0.4865052931160742</v>
       </c>
       <c r="G50">
-        <v>-3.939006045703432</v>
+        <v>-5.421822818884271</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.094785738288024</v>
       </c>
       <c r="E51">
-        <v>-10.28570048621422</v>
+        <v>-13.98987490902495</v>
       </c>
       <c r="F51">
-        <v>0.1224806001956216</v>
+        <v>-0.5035191312021733</v>
       </c>
       <c r="G51">
-        <v>-2.740144297230438</v>
+        <v>-5.76349879575704</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.568439078577979</v>
       </c>
       <c r="E52">
-        <v>-11.46477226206509</v>
+        <v>-13.33887564670337</v>
       </c>
       <c r="F52">
-        <v>0.1276462993194793</v>
+        <v>-0.5351693929283368</v>
       </c>
       <c r="G52">
-        <v>-3.395020859720703</v>
+        <v>-5.431294600260831</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.087321735788292</v>
       </c>
       <c r="E53">
-        <v>-9.131685034286036</v>
+        <v>-13.43268007768595</v>
       </c>
       <c r="F53">
-        <v>0.5066310130394754</v>
+        <v>-0.330702638527932</v>
       </c>
       <c r="G53">
-        <v>-3.524252716980811</v>
+        <v>-5.983532349896068</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.653154479495512</v>
       </c>
       <c r="E54">
-        <v>-8.950729616863256</v>
+        <v>-13.1039243288465</v>
       </c>
       <c r="F54">
-        <v>0.1141439106538473</v>
+        <v>-0.3150299272669653</v>
       </c>
       <c r="G54">
-        <v>-3.38420193413513</v>
+        <v>-6.325722643453287</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.258209877388157</v>
       </c>
       <c r="E55">
-        <v>-8.990687663019431</v>
+        <v>-12.42734959118663</v>
       </c>
       <c r="F55">
-        <v>0.1041049260993201</v>
+        <v>-0.2626862194514674</v>
       </c>
       <c r="G55">
-        <v>-4.202780014721972</v>
+        <v>-6.263103934435434</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.89848937059651</v>
       </c>
       <c r="E56">
-        <v>-8.183087414483872</v>
+        <v>-11.21967464894166</v>
       </c>
       <c r="F56">
-        <v>-0.3895457169857949</v>
+        <v>-0.3295122745701091</v>
       </c>
       <c r="G56">
-        <v>-4.087646178253876</v>
+        <v>-6.715921919296487</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.571097040645062</v>
       </c>
       <c r="E57">
-        <v>-7.690749131193397</v>
+        <v>-11.13064641098264</v>
       </c>
       <c r="F57">
-        <v>0.2003264268737051</v>
+        <v>-0.2912831189309119</v>
       </c>
       <c r="G57">
-        <v>-4.944281082745376</v>
+        <v>-6.608763907554242</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.264666923409322</v>
       </c>
       <c r="E58">
-        <v>-8.41651035057321</v>
+        <v>-9.565442271839803</v>
       </c>
       <c r="F58">
-        <v>0.07267418173489848</v>
+        <v>-0.1780999672168043</v>
       </c>
       <c r="G58">
-        <v>-4.910469329545868</v>
+        <v>-7.187427613940729</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.980449021395104</v>
       </c>
       <c r="E59">
-        <v>-7.103306461775674</v>
+        <v>-10.14052083114351</v>
       </c>
       <c r="F59">
-        <v>-0.3238131068388485</v>
+        <v>-0.1111587690291734</v>
       </c>
       <c r="G59">
-        <v>-5.441014402373545</v>
+        <v>-6.475702087978972</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.704756570488684</v>
       </c>
       <c r="E60">
-        <v>-6.007257380308122</v>
+        <v>-9.881775765606694</v>
       </c>
       <c r="F60">
-        <v>0.4335159925987799</v>
+        <v>-0.261282965071125</v>
       </c>
       <c r="G60">
-        <v>-5.592434977913524</v>
+        <v>-7.0544415059586</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.432654511269352</v>
       </c>
       <c r="E61">
-        <v>-6.432965694314372</v>
+        <v>-9.021770296574449</v>
       </c>
       <c r="F61">
-        <v>-0.1070426114046627</v>
+        <v>-0.4218470754905588</v>
       </c>
       <c r="G61">
-        <v>-5.547454459353234</v>
+        <v>-7.468617860126585</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.15345669925721</v>
       </c>
       <c r="E62">
-        <v>-5.390704852714675</v>
+        <v>-8.526915167221127</v>
       </c>
       <c r="F62">
-        <v>-0.07158931493224663</v>
+        <v>-0.6781953086956994</v>
       </c>
       <c r="G62">
-        <v>-5.073348463096243</v>
+        <v>-7.450838689461103</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.85368790000111</v>
       </c>
       <c r="E63">
-        <v>-6.250552499716578</v>
+        <v>-7.753155284560271</v>
       </c>
       <c r="F63">
-        <v>-0.293538763368735</v>
+        <v>-0.2894573971751418</v>
       </c>
       <c r="G63">
-        <v>-5.394360396530351</v>
+        <v>-7.439160828905054</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.52810704589924</v>
       </c>
       <c r="E64">
-        <v>-5.021945372394474</v>
+        <v>-7.511243184522983</v>
       </c>
       <c r="F64">
-        <v>-0.5236849072559244</v>
+        <v>-0.7537995731818075</v>
       </c>
       <c r="G64">
-        <v>-5.589192433131362</v>
+        <v>-7.129547406355747</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.15992325025576</v>
       </c>
       <c r="E65">
-        <v>-5.158237155230047</v>
+        <v>-7.498575889982256</v>
       </c>
       <c r="F65">
-        <v>-0.188322849334753</v>
+        <v>-0.4835737008775667</v>
       </c>
       <c r="G65">
-        <v>-5.469596834157054</v>
+        <v>-7.40310644610178</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.74497507806011</v>
       </c>
       <c r="E66">
-        <v>-3.908253449219051</v>
+        <v>-8.386304044607732</v>
       </c>
       <c r="F66">
-        <v>-0.2732023436300071</v>
+        <v>-0.7982116631155002</v>
       </c>
       <c r="G66">
-        <v>-5.594842084426531</v>
+        <v>-7.556304938708307</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.27209349755352</v>
       </c>
       <c r="E67">
-        <v>-4.92297434652381</v>
+        <v>-7.639257617188173</v>
       </c>
       <c r="F67">
-        <v>0.02121268520338199</v>
+        <v>-0.9642984990093982</v>
       </c>
       <c r="G67">
-        <v>-5.883347636956687</v>
+        <v>-7.285570724609859</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.73361110518429</v>
       </c>
       <c r="E68">
-        <v>-5.490431763046458</v>
+        <v>-7.66995400208998</v>
       </c>
       <c r="F68">
-        <v>-0.5346856263651019</v>
+        <v>-0.9188343824741502</v>
       </c>
       <c r="G68">
-        <v>-5.169084467252367</v>
+        <v>-7.483418171213606</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.12696311186839</v>
       </c>
       <c r="E69">
-        <v>-3.941520671930927</v>
+        <v>-7.090826061744564</v>
       </c>
       <c r="F69">
-        <v>-0.6898951698928396</v>
+        <v>-0.9847542036541292</v>
       </c>
       <c r="G69">
-        <v>-6.439833068041666</v>
+        <v>-7.187419781706955</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.44253121034211</v>
       </c>
       <c r="E70">
-        <v>-6.211524772897164</v>
+        <v>-7.037137498948505</v>
       </c>
       <c r="F70">
-        <v>-0.6531206274129584</v>
+        <v>-0.9171362292984112</v>
       </c>
       <c r="G70">
-        <v>-5.839019804544175</v>
+        <v>-6.873608281855138</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.68401594267386</v>
       </c>
       <c r="E71">
-        <v>-4.158218626015182</v>
+        <v>-6.971549985706813</v>
       </c>
       <c r="F71">
-        <v>-0.8644694581958214</v>
+        <v>-1.002854031405298</v>
       </c>
       <c r="G71">
-        <v>-5.211018246874829</v>
+        <v>-6.720934548911424</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.8503631898642</v>
       </c>
       <c r="E72">
-        <v>-4.944122498589837</v>
+        <v>-7.251991427204535</v>
       </c>
       <c r="F72">
-        <v>-1.186099669680786</v>
+        <v>-1.107762621132842</v>
       </c>
       <c r="G72">
-        <v>-4.787205634421045</v>
+        <v>-7.404286502656963</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.94439786399495</v>
       </c>
       <c r="E73">
-        <v>-5.368705292327059</v>
+        <v>-7.454190520553813</v>
       </c>
       <c r="F73">
-        <v>-1.174865350964019</v>
+        <v>-1.387320880597022</v>
       </c>
       <c r="G73">
-        <v>-4.71996068598774</v>
+        <v>-6.815699356079655</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.97308500395587</v>
       </c>
       <c r="E74">
-        <v>-6.193196651320696</v>
+        <v>-6.93542950681478</v>
       </c>
       <c r="F74">
-        <v>-1.476338898436662</v>
+        <v>-1.145248731211728</v>
       </c>
       <c r="G74">
-        <v>-5.029177275359197</v>
+        <v>-7.17080239238452</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.93825712106776</v>
       </c>
       <c r="E75">
-        <v>-4.794548745937462</v>
+        <v>-7.217366104389439</v>
       </c>
       <c r="F75">
-        <v>-0.9084408566712248</v>
+        <v>-1.243906460517746</v>
       </c>
       <c r="G75">
-        <v>-4.137506178454958</v>
+        <v>-7.081159866104054</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.84630401944389</v>
       </c>
       <c r="E76">
-        <v>-7.706701615892063</v>
+        <v>-7.983160127729275</v>
       </c>
       <c r="F76">
-        <v>-0.9946142608496518</v>
+        <v>-1.109220547761769</v>
       </c>
       <c r="G76">
-        <v>-4.844981412222382</v>
+        <v>-6.493327224713577</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.69932216136035</v>
       </c>
       <c r="E77">
-        <v>-6.052033151601099</v>
+        <v>-8.125523905521748</v>
       </c>
       <c r="F77">
-        <v>-0.735122373350887</v>
+        <v>-1.381472606733257</v>
       </c>
       <c r="G77">
-        <v>-4.201620844123517</v>
+        <v>-5.989299484697837</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.49326924205385</v>
       </c>
       <c r="E78">
-        <v>-7.115670571889688</v>
+        <v>-9.425861145634967</v>
       </c>
       <c r="F78">
-        <v>-1.32788634781356</v>
+        <v>-1.712708566621084</v>
       </c>
       <c r="G78">
-        <v>-4.123718836269288</v>
+        <v>-5.667410341081116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-14.22782644451127</v>
       </c>
       <c r="E79">
-        <v>-6.746084602515846</v>
+        <v>-8.285472380063545</v>
       </c>
       <c r="F79">
-        <v>-1.212848481484584</v>
+        <v>-1.316907166256855</v>
       </c>
       <c r="G79">
-        <v>-3.649213396089857</v>
+        <v>-5.171188727392805</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.89209423636571</v>
       </c>
       <c r="E80">
-        <v>-8.622904187360565</v>
+        <v>-9.369526987224992</v>
       </c>
       <c r="F80">
-        <v>-0.9694658548680616</v>
+        <v>-1.273043455543816</v>
       </c>
       <c r="G80">
-        <v>-3.122200660693956</v>
+        <v>-5.10924359047946</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.48052869286853</v>
       </c>
       <c r="E81">
-        <v>-9.226253656152382</v>
+        <v>-11.29342737564797</v>
       </c>
       <c r="F81">
-        <v>-1.305952007354832</v>
+        <v>-1.546665634199535</v>
       </c>
       <c r="G81">
-        <v>-3.020757568861658</v>
+        <v>-4.45161269244557</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.98731738837034</v>
       </c>
       <c r="E82">
-        <v>-10.77788094747435</v>
+        <v>-10.96965548039831</v>
       </c>
       <c r="F82">
-        <v>-1.249473917831962</v>
+        <v>-1.549345402747591</v>
       </c>
       <c r="G82">
-        <v>-3.069155552091716</v>
+        <v>-4.659213880841716</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.40574287223123</v>
       </c>
       <c r="E83">
-        <v>-10.49596926916764</v>
+        <v>-12.42716684988834</v>
       </c>
       <c r="F83">
-        <v>-1.547071534226906</v>
+        <v>-1.525830537284321</v>
       </c>
       <c r="G83">
-        <v>-1.572572322681936</v>
+        <v>-3.641156638281681</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.74054299666234</v>
       </c>
       <c r="E84">
-        <v>-11.73772961675547</v>
+        <v>-13.85963850830097</v>
       </c>
       <c r="F84">
-        <v>-1.185659806589899</v>
+        <v>-1.3278391308716</v>
       </c>
       <c r="G84">
-        <v>-2.368175850866981</v>
+        <v>-3.294003319256757</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.9880465287944</v>
       </c>
       <c r="E85">
-        <v>-13.12258470732895</v>
+        <v>-14.4997895826421</v>
       </c>
       <c r="F85">
-        <v>-1.202835176319544</v>
+        <v>-1.594109548827473</v>
       </c>
       <c r="G85">
-        <v>-1.795563850442695</v>
+        <v>-3.17413098135579</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.16252110713049</v>
       </c>
       <c r="E86">
-        <v>-13.16562858949948</v>
+        <v>-15.33545308009952</v>
       </c>
       <c r="F86">
-        <v>-1.479678047437347</v>
+        <v>-1.148058553442024</v>
       </c>
       <c r="G86">
-        <v>-2.038728601658987</v>
+        <v>-2.424588819991757</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.28032568472886</v>
       </c>
       <c r="E87">
-        <v>-16.18310689865173</v>
+        <v>-16.00269139870118</v>
       </c>
       <c r="F87">
-        <v>-1.374781883220846</v>
+        <v>-1.780227136888467</v>
       </c>
       <c r="G87">
-        <v>-1.453749504106597</v>
+        <v>-2.426821006617159</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.365873934463421</v>
       </c>
       <c r="E88">
-        <v>-16.12448432080177</v>
+        <v>-16.8590295821336</v>
       </c>
       <c r="F88">
-        <v>-1.36736219639397</v>
+        <v>-1.802026453460538</v>
       </c>
       <c r="G88">
-        <v>-1.370375375589395</v>
+        <v>-1.951015415631354</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.455145004843791</v>
       </c>
       <c r="E89">
-        <v>-18.49130808417241</v>
+        <v>-18.2004296226154</v>
       </c>
       <c r="F89">
-        <v>-1.571141405850052</v>
+        <v>-1.8732080643831</v>
       </c>
       <c r="G89">
-        <v>-2.059551900517707</v>
+        <v>-1.908019062960309</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.57580807818209</v>
       </c>
       <c r="E90">
-        <v>-21.06535632659537</v>
+        <v>-20.31063476464753</v>
       </c>
       <c r="F90">
-        <v>-1.648865462519924</v>
+        <v>-1.770322347853193</v>
       </c>
       <c r="G90">
-        <v>-0.1850973312239628</v>
+        <v>-1.125017598916568</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.771469243406356</v>
       </c>
       <c r="E91">
-        <v>-21.99104067951846</v>
+        <v>-21.48447764744045</v>
       </c>
       <c r="F91">
-        <v>-2.078586851293987</v>
+        <v>-2.003443159083835</v>
       </c>
       <c r="G91">
-        <v>-0.8612645158547572</v>
+        <v>-1.067918003964329</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.073599178031295</v>
       </c>
       <c r="E92">
-        <v>-22.5968862283165</v>
+        <v>-23.52673625219839</v>
       </c>
       <c r="F92">
-        <v>-1.380834763833102</v>
+        <v>-2.224996647901786</v>
       </c>
       <c r="G92">
-        <v>-0.7444493598699843</v>
+        <v>-1.372949569756232</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.515545009800897</v>
       </c>
       <c r="E93">
-        <v>-23.19001879724924</v>
+        <v>-25.32209890332924</v>
       </c>
       <c r="F93">
-        <v>-1.889307384856508</v>
+        <v>-2.527016917860277</v>
       </c>
       <c r="G93">
-        <v>-1.105888673297481</v>
+        <v>-1.070003988892629</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.120273531083571</v>
       </c>
       <c r="E94">
-        <v>-27.56496176828772</v>
+        <v>-27.75397026246934</v>
       </c>
       <c r="F94">
-        <v>-2.254917278490904</v>
+        <v>-2.545298986440062</v>
       </c>
       <c r="G94">
-        <v>-0.7257799252989332</v>
+        <v>-1.279918296996502</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.897587009900176</v>
       </c>
       <c r="E95">
-        <v>-29.22528690640311</v>
+        <v>-29.64664680815226</v>
       </c>
       <c r="F95">
-        <v>-2.221779268909312</v>
+        <v>-2.838172423536841</v>
       </c>
       <c r="G95">
-        <v>-0.7211850148185738</v>
+        <v>-1.370255281338203</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.851820112134047</v>
       </c>
       <c r="E96">
-        <v>-32.00994449510812</v>
+        <v>-31.77353332347057</v>
       </c>
       <c r="F96">
-        <v>-3.075078045430875</v>
+        <v>-3.087458824633116</v>
       </c>
       <c r="G96">
-        <v>-1.337882048408399</v>
+        <v>-0.7969958162553213</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.961981666349657</v>
       </c>
       <c r="E97">
-        <v>-32.30048654654782</v>
+        <v>-33.77417467414806</v>
       </c>
       <c r="F97">
-        <v>-2.341055891238413</v>
+        <v>-3.234644801497338</v>
       </c>
       <c r="G97">
-        <v>-1.3531287968205</v>
+        <v>-1.632410588710253</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.209186479718294</v>
       </c>
       <c r="E98">
-        <v>-35.4753653350941</v>
+        <v>-35.37894230437121</v>
       </c>
       <c r="F98">
-        <v>-3.232850557702874</v>
+        <v>-3.768447240963547</v>
       </c>
       <c r="G98">
-        <v>-2.115883936560158</v>
+        <v>-1.741417007623006</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.545406683919995</v>
       </c>
       <c r="E99">
-        <v>-39.83274229883422</v>
+        <v>-37.78261751182706</v>
       </c>
       <c r="F99">
-        <v>-2.689889688231313</v>
+        <v>-3.791662237427003</v>
       </c>
       <c r="G99">
-        <v>-2.323273654644424</v>
+        <v>-2.223081109471269</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.938893540427727</v>
       </c>
       <c r="E100">
-        <v>-41.03503883241353</v>
+        <v>-40.69364278490696</v>
       </c>
       <c r="F100">
-        <v>-3.212620168991704</v>
+        <v>-4.141564628369514</v>
       </c>
       <c r="G100">
-        <v>-2.364518197694832</v>
+        <v>-1.980934548645512</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.320955254691782</v>
       </c>
       <c r="E101">
-        <v>-43.84865468708092</v>
+        <v>-42.51833749101942</v>
       </c>
       <c r="F101">
-        <v>-3.415698579625017</v>
+        <v>-4.090398859000798</v>
       </c>
       <c r="G101">
-        <v>-2.606077340987588</v>
+        <v>-2.22983771647307</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.678249766066572</v>
       </c>
       <c r="E102">
-        <v>-44.61570713345218</v>
+        <v>-44.5197368027637</v>
       </c>
       <c r="F102">
-        <v>-3.280842023184063</v>
+        <v>-4.231879041194537</v>
       </c>
       <c r="G102">
-        <v>-3.218035873144542</v>
+        <v>-3.059451414446548</v>
       </c>
     </row>
   </sheetData>
